--- a/atılisgucu.xlsx
+++ b/atılisgucu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/omerozogul/Desktop/DashboardProje/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\splktfs\Aktif Pasif Yonetimi\Aktif Pasif\PARA PİYASALARI\Reports\APKO\APKO Veriler\github_excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00AAB69-481A-3C4A-8069-DD58D259E114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8960B14A-F866-4031-AC04-26260ADEDEB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" xr2:uid="{13ECF506-27B7-7A4A-BC2A-FF0ACE576F85}"/>
+    <workbookView xWindow="28710" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{13ECF506-27B7-7A4A-BC2A-FF0ACE576F85}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,12 +35,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Tarih</t>
   </si>
   <si>
     <t>Atıl İşgücü</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -101,9 +104,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -141,7 +144,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -247,7 +250,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -389,7 +392,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -397,13 +400,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07957053-AE36-E04B-B39B-C15147CDBE65}">
-  <dimension ref="A1:B144"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B149"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.83203125" style="1"/>
+    <col min="2" max="2" width="10.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -411,7 +414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>41640</v>
       </c>
@@ -419,7 +422,7 @@
         <v>0.193</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>41671</v>
       </c>
@@ -427,7 +430,7 @@
         <v>0.19500000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>41699</v>
       </c>
@@ -435,7 +438,7 @@
         <v>0.17300000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>41730</v>
       </c>
@@ -443,7 +446,7 @@
         <v>0.16200000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>41760</v>
       </c>
@@ -451,7 +454,7 @@
         <v>0.16399999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>41791</v>
       </c>
@@ -459,7 +462,7 @@
         <v>0.16800000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>41821</v>
       </c>
@@ -467,7 +470,7 @@
         <v>0.16699999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>41852</v>
       </c>
@@ -475,7 +478,7 @@
         <v>0.17100000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>41883</v>
       </c>
@@ -483,7 +486,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>41913</v>
       </c>
@@ -491,7 +494,7 @@
         <v>0.17800000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>41944</v>
       </c>
@@ -499,7 +502,7 @@
         <v>0.17399999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>41974</v>
       </c>
@@ -507,7 +510,7 @@
         <v>0.17800000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>42005</v>
       </c>
@@ -515,7 +518,7 @@
         <v>0.19500000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>42036</v>
       </c>
@@ -523,7 +526,7 @@
         <v>0.192</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>42064</v>
       </c>
@@ -531,7 +534,7 @@
         <v>0.17699999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>42095</v>
       </c>
@@ -539,7 +542,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>42125</v>
       </c>
@@ -547,7 +550,7 @@
         <v>0.152</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>42156</v>
       </c>
@@ -555,7 +558,7 @@
         <v>0.16399999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>42186</v>
       </c>
@@ -563,7 +566,7 @@
         <v>0.17300000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>42217</v>
       </c>
@@ -571,7 +574,7 @@
         <v>0.16200000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>42248</v>
       </c>
@@ -579,7 +582,7 @@
         <v>0.17199999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>42278</v>
       </c>
@@ -587,7 +590,7 @@
         <v>0.16200000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>42309</v>
       </c>
@@ -595,7 +598,7 @@
         <v>0.16800000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>42339</v>
       </c>
@@ -603,7 +606,7 @@
         <v>0.17800000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>42370</v>
       </c>
@@ -611,7 +614,7 @@
         <v>0.192</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>42401</v>
       </c>
@@ -619,7 +622,7 @@
         <v>0.183</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>42430</v>
       </c>
@@ -627,7 +630,7 @@
         <v>0.16699999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>42461</v>
       </c>
@@ -635,7 +638,7 @@
         <v>0.159</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>42491</v>
       </c>
@@ -643,7 +646,7 @@
         <v>0.152</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>42522</v>
       </c>
@@ -651,7 +654,7 @@
         <v>0.16600000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>42552</v>
       </c>
@@ -659,7 +662,7 @@
         <v>0.184</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>42583</v>
       </c>
@@ -667,7 +670,7 @@
         <v>0.17399999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>42614</v>
       </c>
@@ -675,7 +678,7 @@
         <v>0.182</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>42644</v>
       </c>
@@ -683,7 +686,7 @@
         <v>0.183</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>42675</v>
       </c>
@@ -691,7 +694,7 @@
         <v>0.17899999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>42705</v>
       </c>
@@ -699,7 +702,7 @@
         <v>0.191</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>42736</v>
       </c>
@@ -707,7 +710,7 @@
         <v>0.20499999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>42767</v>
       </c>
@@ -715,7 +718,7 @@
         <v>0.19500000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>42795</v>
       </c>
@@ -723,7 +726,7 @@
         <v>0.17899999999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>42826</v>
       </c>
@@ -731,7 +734,7 @@
         <v>0.16500000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>42856</v>
       </c>
@@ -739,7 +742,7 @@
         <v>0.154</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>42887</v>
       </c>
@@ -747,7 +750,7 @@
         <v>0.158</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>42917</v>
       </c>
@@ -755,7 +758,7 @@
         <v>0.159</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>42948</v>
       </c>
@@ -763,7 +766,7 @@
         <v>0.161</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>42979</v>
       </c>
@@ -771,7 +774,7 @@
         <v>0.153</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>43009</v>
       </c>
@@ -779,7 +782,7 @@
         <v>0.158</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>43040</v>
       </c>
@@ -787,7 +790,7 @@
         <v>0.16200000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>43070</v>
       </c>
@@ -795,7 +798,7 @@
         <v>0.16600000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>43101</v>
       </c>
@@ -803,7 +806,7 @@
         <v>0.17800000000000002</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>43132</v>
       </c>
@@ -811,7 +814,7 @@
         <v>0.17100000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>43160</v>
       </c>
@@ -819,7 +822,7 @@
         <v>0.157</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>43191</v>
       </c>
@@ -827,7 +830,7 @@
         <v>0.14599999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>43221</v>
       </c>
@@ -835,7 +838,7 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>43252</v>
       </c>
@@ -843,7 +846,7 @@
         <v>0.158</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>43282</v>
       </c>
@@ -851,7 +854,7 @@
         <v>0.161</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>43313</v>
       </c>
@@ -859,7 +862,7 @@
         <v>0.16500000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>43344</v>
       </c>
@@ -867,7 +870,7 @@
         <v>0.161</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>43374</v>
       </c>
@@ -875,7 +878,7 @@
         <v>0.17100000000000001</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>43405</v>
       </c>
@@ -883,7 +886,7 @@
         <v>0.17399999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>43435</v>
       </c>
@@ -891,7 +894,7 @@
         <v>0.188</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>43466</v>
       </c>
@@ -899,7 +902,7 @@
         <v>0.21299999999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>43497</v>
       </c>
@@ -907,7 +910,7 @@
         <v>0.20399999999999999</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>43525</v>
       </c>
@@ -915,7 +918,7 @@
         <v>0.19699999999999998</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>43556</v>
       </c>
@@ -923,7 +926,7 @@
         <v>0.182</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>43586</v>
       </c>
@@ -931,7 +934,7 @@
         <v>0.17399999999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>43617</v>
       </c>
@@ -939,7 +942,7 @@
         <v>0.188</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>43647</v>
       </c>
@@ -947,7 +950,7 @@
         <v>0.193</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>43678</v>
       </c>
@@ -955,7 +958,7 @@
         <v>0.193</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>43709</v>
       </c>
@@ -963,7 +966,7 @@
         <v>0.188</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>43739</v>
       </c>
@@ -971,7 +974,7 @@
         <v>0.185</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>43770</v>
       </c>
@@ -979,7 +982,7 @@
         <v>0.18100000000000002</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>43800</v>
       </c>
@@ -987,7 +990,7 @@
         <v>0.18899999999999997</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>43831</v>
       </c>
@@ -995,7 +998,7 @@
         <v>0.22500000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>43862</v>
       </c>
@@ -1003,7 +1006,7 @@
         <v>0.217</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>43891</v>
       </c>
@@ -1011,7 +1014,7 @@
         <v>0.23300000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>43922</v>
       </c>
@@ -1019,7 +1022,7 @@
         <v>0.27300000000000002</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>43952</v>
       </c>
@@ -1027,7 +1030,7 @@
         <v>0.28699999999999998</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>43983</v>
       </c>
@@ -1035,7 +1038,7 @@
         <v>0.254</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>44013</v>
       </c>
@@ -1043,7 +1046,7 @@
         <v>0.26100000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>44044</v>
       </c>
@@ -1051,7 +1054,7 @@
         <v>0.249</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>44075</v>
       </c>
@@ -1059,7 +1062,7 @@
         <v>0.23699999999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>44105</v>
       </c>
@@ -1067,7 +1070,7 @@
         <v>0.253</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>44136</v>
       </c>
@@ -1075,7 +1078,7 @@
         <v>0.26600000000000001</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>44166</v>
       </c>
@@ -1083,7 +1086,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>44197</v>
       </c>
@@ -1091,7 +1094,7 @@
         <v>0.30199999999999999</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>44228</v>
       </c>
@@ -1099,7 +1102,7 @@
         <v>0.28899999999999998</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>44256</v>
       </c>
@@ -1107,7 +1110,7 @@
         <v>0.25800000000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>44287</v>
       </c>
@@ -1115,7 +1118,7 @@
         <v>0.26700000000000002</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>44317</v>
       </c>
@@ -1123,7 +1126,7 @@
         <v>0.26600000000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>44348</v>
       </c>
@@ -1131,7 +1134,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>44378</v>
       </c>
@@ -1139,7 +1142,7 @@
         <v>0.23499999999999999</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>44409</v>
       </c>
@@ -1147,7 +1150,7 @@
         <v>0.217</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>44440</v>
       </c>
@@ -1155,7 +1158,7 @@
         <v>0.21299999999999999</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>44470</v>
       </c>
@@ -1163,7 +1166,7 @@
         <v>0.222</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>44501</v>
       </c>
@@ -1171,7 +1174,7 @@
         <v>0.21899999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>44531</v>
       </c>
@@ -1179,7 +1182,7 @@
         <v>0.22899999999999998</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>44562</v>
       </c>
@@ -1187,7 +1190,7 @@
         <v>0.23699999999999999</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>44593</v>
       </c>
@@ -1195,7 +1198,7 @@
         <v>0.22500000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>44621</v>
       </c>
@@ -1203,7 +1206,7 @@
         <v>0.22699999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>44652</v>
       </c>
@@ -1211,7 +1214,7 @@
         <v>0.21299999999999999</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>44682</v>
       </c>
@@ -1219,7 +1222,7 @@
         <v>0.217</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>44713</v>
       </c>
@@ -1227,7 +1230,7 @@
         <v>0.19800000000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>44743</v>
       </c>
@@ -1235,7 +1238,7 @@
         <v>0.22899999999999998</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>44774</v>
       </c>
@@ -1243,7 +1246,7 @@
         <v>0.19800000000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>44805</v>
       </c>
@@ -1251,7 +1254,7 @@
         <v>0.19899999999999998</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>44835</v>
       </c>
@@ -1259,7 +1262,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>44866</v>
       </c>
@@ -1267,7 +1270,7 @@
         <v>0.20399999999999999</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>44896</v>
       </c>
@@ -1275,7 +1278,7 @@
         <v>0.21600000000000003</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>44927</v>
       </c>
@@ -1283,7 +1286,7 @@
         <v>0.22600000000000001</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>44958</v>
       </c>
@@ -1291,7 +1294,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>44986</v>
       </c>
@@ -1299,7 +1302,7 @@
         <v>0.22399999999999998</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>45017</v>
       </c>
@@ -1307,7 +1310,7 @@
         <v>0.23899999999999999</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>45047</v>
       </c>
@@ -1315,7 +1318,7 @@
         <v>0.21899999999999997</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>45078</v>
       </c>
@@ -1323,7 +1326,7 @@
         <v>0.23600000000000002</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>45108</v>
       </c>
@@ -1331,7 +1334,7 @@
         <v>0.22800000000000001</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>45139</v>
       </c>
@@ -1339,7 +1342,7 @@
         <v>0.22800000000000001</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>45170</v>
       </c>
@@ -1347,7 +1350,7 @@
         <v>0.215</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>45200</v>
       </c>
@@ -1355,7 +1358,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>45231</v>
       </c>
@@ -1363,7 +1366,7 @@
         <v>0.22399999999999998</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>45261</v>
       </c>
@@ -1371,7 +1374,7 @@
         <v>0.248</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>45292</v>
       </c>
@@ -1379,7 +1382,7 @@
         <v>0.27300000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>45323</v>
       </c>
@@ -1387,7 +1390,7 @@
         <v>0.249</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>45352</v>
       </c>
@@ -1395,7 +1398,7 @@
         <v>0.24399999999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>45383</v>
       </c>
@@ -1403,7 +1406,7 @@
         <v>0.27399999999999997</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>45413</v>
       </c>
@@ -1411,7 +1414,7 @@
         <v>0.24600000000000002</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>45444</v>
       </c>
@@ -1419,7 +1422,7 @@
         <v>0.28899999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>45474</v>
       </c>
@@ -1427,7 +1430,7 @@
         <v>0.26899999999999996</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>45505</v>
       </c>
@@ -1435,7 +1438,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>45536</v>
       </c>
@@ -1443,7 +1446,7 @@
         <v>0.255</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>45566</v>
       </c>
@@ -1451,7 +1454,7 @@
         <v>0.27399999999999997</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>45597</v>
       </c>
@@ -1459,7 +1462,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>45627</v>
       </c>
@@ -1467,7 +1470,7 @@
         <v>0.28600000000000003</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>45658</v>
       </c>
@@ -1475,7 +1478,7 @@
         <v>0.29399999999999998</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>45689</v>
       </c>
@@ -1483,7 +1486,7 @@
         <v>0.29499999999999998</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>45717</v>
       </c>
@@ -1491,7 +1494,7 @@
         <v>0.29299999999999998</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>45748</v>
       </c>
@@ -1499,7 +1502,7 @@
         <v>0.32100000000000001</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>45778</v>
       </c>
@@ -1507,7 +1510,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>45809</v>
       </c>
@@ -1515,7 +1518,7 @@
         <v>0.32600000000000001</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>45839</v>
       </c>
@@ -1523,7 +1526,7 @@
         <v>0.29399999999999998</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>45870</v>
       </c>
@@ -1531,7 +1534,7 @@
         <v>0.29100000000000004</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>45901</v>
       </c>
@@ -1539,7 +1542,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
         <v>45931</v>
       </c>
@@ -1547,15 +1550,34 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
         <v>45962</v>
       </c>
       <c r="B144" s="1">
         <v>0.28899999999999998</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B145" s="1">
+        <v>0.28599999999999998</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B149" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{9e923255-b694-4734-b055-efbd556a65fc}" enabled="1" method="Standard" siteId="{a71b8764-0a7a-4511-8f04-04867f0718ab}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>